--- a/UHNW_Portfolio_Analysis.xlsx
+++ b/UHNW_Portfolio_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mario/jpmproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD284E2-5E9B-AE4D-8D90-CC1F7B7E65D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E689B2-D83F-EE4C-99D5-93D4FA59D4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30160" yWindow="-3000" windowWidth="33500" windowHeight="19020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -821,9 +821,6 @@
     <t>Transfer appreciated stock into CRT. Avoid immediate gain, receive income stream, estate planning benefit.</t>
   </si>
   <si>
-    <t>All tax figures are estimates. Actual liability depends on cost basis, holding period, filing status, and applicable deductions. Coordinate with qualified CPA and estate attorney before execution.  Change portfolio value, cost basis, or tax rates in the Inputs tab to update all figures.</t>
-  </si>
-  <si>
     <t>SECURITIES-BASED LENDING (SBL) CREDIT FACILITY</t>
   </si>
   <si>
@@ -1362,6 +1359,9 @@
   </si>
   <si>
     <t>Foundation value = Seed × (1 + Net Return)^Year + Annual Contribution × ((1 + Net Return)^Year − 1) / Net Return.  Net Return = Foundation Annual Return − Annual Payout (Inputs C36 &amp; C37).  Annual Contribution (Inputs C38, default $70,760) sourced from diversified portfolio income ($625K/yr).  Cumulative grants column is a simplified lower-bound: Seed × Payout × Years.</t>
+  </si>
+  <si>
+    <t>All tax figures are estimates. Actual liability depends on cost basis, holding period, filing status, and applicable deductions.</t>
   </si>
 </sst>
 </file>
@@ -1962,22 +1962,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2298,7 +2298,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="101" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="97" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B2" s="98"/>
       <c r="C2" s="98"/>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     <row r="52" spans="2:5" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="53" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="100" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C53" s="98"/>
       <c r="D53" s="98"/>
@@ -3217,7 +3217,7 @@
     <row r="30" spans="2:5" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="2:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="100" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C31" s="98"/>
       <c r="D31" s="98"/>
@@ -3225,6 +3225,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
@@ -3236,12 +3242,6 @@
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C29:E29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3924,7 +3924,7 @@
         <f>Inputs!C6</f>
         <v>25000000</v>
       </c>
-      <c r="D6" s="108" t="s">
+      <c r="D6" s="109" t="s">
         <v>220</v>
       </c>
       <c r="E6" s="98"/>
@@ -3937,7 +3937,7 @@
         <f>Inputs!C7</f>
         <v>6500000</v>
       </c>
-      <c r="D7" s="110" t="s">
+      <c r="D7" s="111" t="s">
         <v>221</v>
       </c>
       <c r="E7" s="98"/>
@@ -3950,7 +3950,7 @@
         <f>Inputs!C40</f>
         <v>18500000</v>
       </c>
-      <c r="D8" s="108" t="s">
+      <c r="D8" s="109" t="s">
         <v>222</v>
       </c>
       <c r="E8" s="98"/>
@@ -3963,7 +3963,7 @@
         <f>Inputs!C12</f>
         <v>0.2</v>
       </c>
-      <c r="D9" s="110" t="s">
+      <c r="D9" s="111" t="s">
         <v>224</v>
       </c>
       <c r="E9" s="98"/>
@@ -3976,7 +3976,7 @@
         <f>Inputs!C13</f>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="D10" s="108" t="s">
+      <c r="D10" s="109" t="s">
         <v>225</v>
       </c>
       <c r="E10" s="98"/>
@@ -3989,7 +3989,7 @@
         <f>Inputs!C14</f>
         <v>0.13300000000000001</v>
       </c>
-      <c r="D11" s="110" t="s">
+      <c r="D11" s="111" t="s">
         <v>227</v>
       </c>
       <c r="E11" s="98"/>
@@ -4002,7 +4002,7 @@
         <f>Inputs!C41</f>
         <v>0.371</v>
       </c>
-      <c r="D12" s="108" t="s">
+      <c r="D12" s="109" t="s">
         <v>229</v>
       </c>
       <c r="E12" s="98"/>
@@ -4015,7 +4015,7 @@
         <f>Inputs!C42</f>
         <v>6863500</v>
       </c>
-      <c r="D13" s="110" t="s">
+      <c r="D13" s="111" t="s">
         <v>230</v>
       </c>
       <c r="E13" s="98"/>
@@ -4028,7 +4028,7 @@
         <f>0-Inputs!C16</f>
         <v>-850000</v>
       </c>
-      <c r="D14" s="108" t="s">
+      <c r="D14" s="109" t="s">
         <v>231</v>
       </c>
       <c r="E14" s="98"/>
@@ -4041,7 +4041,7 @@
         <f>Inputs!C43</f>
         <v>6013500</v>
       </c>
-      <c r="D15" s="110" t="s">
+      <c r="D15" s="111" t="s">
         <v>232</v>
       </c>
       <c r="E15" s="98"/>
@@ -4199,7 +4199,7 @@
         <f>Inputs!C16</f>
         <v>850000</v>
       </c>
-      <c r="D28" s="111" t="s">
+      <c r="D28" s="110" t="s">
         <v>249</v>
       </c>
       <c r="E28" s="98"/>
@@ -4211,7 +4211,7 @@
       <c r="C29" s="55">
         <v>500000</v>
       </c>
-      <c r="D29" s="109" t="s">
+      <c r="D29" s="108" t="s">
         <v>251</v>
       </c>
       <c r="E29" s="98"/>
@@ -4223,7 +4223,7 @@
       <c r="C30" s="56">
         <v>1000000</v>
       </c>
-      <c r="D30" s="111" t="s">
+      <c r="D30" s="110" t="s">
         <v>253</v>
       </c>
       <c r="E30" s="98"/>
@@ -4235,7 +4235,7 @@
       <c r="C31" s="57" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="109" t="s">
+      <c r="D31" s="108" t="s">
         <v>256</v>
       </c>
       <c r="E31" s="98"/>
@@ -4247,7 +4247,7 @@
       <c r="C32" s="58" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="111" t="s">
+      <c r="D32" s="110" t="s">
         <v>258</v>
       </c>
       <c r="E32" s="98"/>
@@ -4255,7 +4255,7 @@
     <row r="33" spans="2:5" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" spans="2:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="100" t="s">
-        <v>259</v>
+        <v>438</v>
       </c>
       <c r="C34" s="98"/>
       <c r="D34" s="98"/>
@@ -4263,6 +4263,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D5:E5"/>
@@ -4279,13 +4286,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4309,7 +4309,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="101" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="97" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B2" s="98"/>
       <c r="C2" s="98"/>
@@ -4332,7 +4332,7 @@
     <row r="3" spans="1:7" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="99" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C4" s="98"/>
       <c r="D4" s="98"/>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="5" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>217</v>
@@ -4354,69 +4354,69 @@
     </row>
     <row r="6" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="59" t="s">
         <v>264</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="D6" s="109" t="s">
         <v>265</v>
-      </c>
-      <c r="D6" s="108" t="s">
-        <v>266</v>
       </c>
       <c r="E6" s="98"/>
       <c r="F6" s="98"/>
     </row>
     <row r="7" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C7" s="60">
         <f>Inputs!C23</f>
         <v>5000000</v>
       </c>
-      <c r="D7" s="110" t="s">
-        <v>268</v>
+      <c r="D7" s="111" t="s">
+        <v>267</v>
       </c>
       <c r="E7" s="98"/>
       <c r="F7" s="98"/>
     </row>
     <row r="8" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" s="61">
         <f>Inputs!C24</f>
         <v>15000000</v>
       </c>
-      <c r="D8" s="108" t="s">
-        <v>270</v>
+      <c r="D8" s="109" t="s">
+        <v>269</v>
       </c>
       <c r="E8" s="98"/>
       <c r="F8" s="98"/>
     </row>
     <row r="9" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="62">
         <f>Inputs!C23/Inputs!C24</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D9" s="110" t="s">
-        <v>272</v>
+      <c r="D9" s="111" t="s">
+        <v>271</v>
       </c>
       <c r="E9" s="98"/>
       <c r="F9" s="98"/>
     </row>
     <row r="10" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C10" s="63">
         <f>Inputs!C27</f>
         <v>0.4</v>
       </c>
-      <c r="D10" s="108" t="s">
-        <v>274</v>
+      <c r="D10" s="109" t="s">
+        <v>273</v>
       </c>
       <c r="E10" s="98"/>
       <c r="F10" s="98"/>
@@ -4429,8 +4429,8 @@
         <f>Inputs!C25</f>
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="D11" s="110" t="s">
-        <v>275</v>
+      <c r="D11" s="111" t="s">
+        <v>274</v>
       </c>
       <c r="E11" s="98"/>
       <c r="F11" s="98"/>
@@ -4443,103 +4443,103 @@
         <f>Inputs!C26</f>
         <v>0.02</v>
       </c>
-      <c r="D12" s="108" t="s">
-        <v>276</v>
+      <c r="D12" s="109" t="s">
+        <v>275</v>
       </c>
       <c r="E12" s="98"/>
       <c r="F12" s="98"/>
     </row>
     <row r="13" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C13" s="65">
         <f>Inputs!C44</f>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="D13" s="110" t="s">
-        <v>278</v>
+      <c r="D13" s="111" t="s">
+        <v>277</v>
       </c>
       <c r="E13" s="98"/>
       <c r="F13" s="98"/>
     </row>
     <row r="14" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C14" s="65">
         <f>Inputs!C45</f>
         <v>4.095E-2</v>
       </c>
-      <c r="D14" s="108" t="s">
-        <v>280</v>
+      <c r="D14" s="109" t="s">
+        <v>279</v>
       </c>
       <c r="E14" s="98"/>
       <c r="F14" s="98"/>
     </row>
     <row r="15" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15" s="66" t="s">
         <v>281</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="D15" s="111" t="s">
         <v>282</v>
-      </c>
-      <c r="D15" s="110" t="s">
-        <v>283</v>
       </c>
       <c r="E15" s="98"/>
       <c r="F15" s="98"/>
     </row>
     <row r="16" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="59" t="s">
         <v>284</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="D16" s="109" t="s">
         <v>285</v>
-      </c>
-      <c r="D16" s="108" t="s">
-        <v>286</v>
       </c>
       <c r="E16" s="98"/>
       <c r="F16" s="98"/>
     </row>
     <row r="17" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C17" s="60">
         <f>Inputs!C46</f>
         <v>325000</v>
       </c>
-      <c r="D17" s="110" t="s">
-        <v>288</v>
+      <c r="D17" s="111" t="s">
+        <v>287</v>
       </c>
       <c r="E17" s="98"/>
       <c r="F17" s="98"/>
     </row>
     <row r="18" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C18" s="60">
         <f>Inputs!C47</f>
         <v>204750</v>
       </c>
-      <c r="D18" s="108" t="s">
-        <v>290</v>
+      <c r="D18" s="109" t="s">
+        <v>289</v>
       </c>
       <c r="E18" s="98"/>
       <c r="F18" s="98"/>
     </row>
     <row r="19" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C19" s="66" t="s">
         <v>291</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="D19" s="111" t="s">
         <v>292</v>
-      </c>
-      <c r="D19" s="110" t="s">
-        <v>293</v>
       </c>
       <c r="E19" s="98"/>
       <c r="F19" s="98"/>
@@ -4547,7 +4547,7 @@
     <row r="20" spans="2:6" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="99" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C21" s="98"/>
       <c r="D21" s="98"/>
@@ -4556,24 +4556,24 @@
     </row>
     <row r="22" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C23" s="46">
         <f>Inputs!C23</f>
@@ -4593,7 +4593,7 @@
     </row>
     <row r="24" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C24" s="46">
         <f>Inputs!C23</f>
@@ -4613,7 +4613,7 @@
     </row>
     <row r="25" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C25" s="46">
         <f>Inputs!C23</f>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="26" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C26" s="46">
         <f>Inputs!C23</f>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="27" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C27" s="46">
         <f>Inputs!C23</f>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="28" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C28" s="46">
         <f>Inputs!C23</f>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="29" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C29" s="46">
         <f>Inputs!C23</f>
@@ -4713,7 +4713,7 @@
     </row>
     <row r="30" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C30" s="46">
         <f>Inputs!C23</f>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="31" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C31" s="46">
         <f>Inputs!C23</f>
@@ -4753,7 +4753,7 @@
     </row>
     <row r="32" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C32" s="46">
         <f>Inputs!C23</f>
@@ -4773,7 +4773,7 @@
     </row>
     <row r="33" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C33" s="46">
         <f>Inputs!C23</f>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="34" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C34" s="69">
         <f>Inputs!C23</f>
@@ -4813,7 +4813,7 @@
     </row>
     <row r="35" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="40" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C35" s="42">
         <f>Inputs!C23</f>
@@ -4833,7 +4833,7 @@
     </row>
     <row r="37" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="99" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C37" s="98"/>
       <c r="D37" s="98"/>
@@ -4842,27 +4842,27 @@
     </row>
     <row r="38" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>319</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>320</v>
       </c>
       <c r="D39" s="61">
         <f>Inputs!C24*(1-0)</f>
@@ -4879,10 +4879,10 @@
     </row>
     <row r="40" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>321</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>322</v>
       </c>
       <c r="D40" s="61">
         <f>Inputs!C24*(1-0.1)</f>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>323</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>324</v>
       </c>
       <c r="D41" s="61">
         <f>Inputs!C24*(1-0.2)</f>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="42" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>325</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>326</v>
       </c>
       <c r="D42" s="61">
         <f>Inputs!C24*(1-0.3)</f>
@@ -4939,10 +4939,10 @@
     </row>
     <row r="43" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>327</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>328</v>
       </c>
       <c r="D43" s="61">
         <f>Inputs!C24*(1-0.4)</f>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C44" s="20" t="s">
         <v>329</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>330</v>
       </c>
       <c r="D44" s="61">
         <f>Inputs!C24*(1-0.5)</f>
@@ -4980,7 +4980,7 @@
     <row r="45" spans="2:6" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="46" spans="2:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C46" s="98"/>
       <c r="D46" s="98"/>
@@ -4989,7 +4989,7 @@
     </row>
     <row r="48" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="99" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C48" s="98"/>
       <c r="D48" s="98"/>
@@ -4998,54 +4998,54 @@
     </row>
     <row r="49" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="105" t="s">
         <v>335</v>
-      </c>
-      <c r="E49" s="105" t="s">
-        <v>336</v>
       </c>
       <c r="F49" s="107"/>
     </row>
     <row r="50" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="16" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C50" s="74">
         <f>Inputs!C23*Inputs!C41</f>
         <v>1855000</v>
       </c>
       <c r="D50" s="59" t="s">
+        <v>337</v>
+      </c>
+      <c r="E50" s="113" t="s">
         <v>338</v>
-      </c>
-      <c r="E50" s="112" t="s">
-        <v>339</v>
       </c>
       <c r="F50" s="98"/>
     </row>
     <row r="51" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C51" s="66" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D51" s="75">
         <f>Inputs!C47</f>
         <v>204750</v>
       </c>
-      <c r="E51" s="113" t="s">
-        <v>341</v>
+      <c r="E51" s="112" t="s">
+        <v>340</v>
       </c>
       <c r="F51" s="98"/>
     </row>
     <row r="52" spans="2:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C52" s="74">
         <f>Inputs!C23*(1-Inputs!C41)</f>
@@ -5055,14 +5055,14 @@
         <f>Inputs!C23</f>
         <v>5000000</v>
       </c>
-      <c r="E52" s="112" t="s">
-        <v>343</v>
+      <c r="E52" s="113" t="s">
+        <v>342</v>
       </c>
       <c r="F52" s="98"/>
     </row>
     <row r="53" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C53" s="74">
         <f>Inputs!C6-Inputs!C23</f>
@@ -5072,77 +5072,77 @@
         <f>Inputs!C6</f>
         <v>25000000</v>
       </c>
-      <c r="E53" s="113" t="s">
-        <v>345</v>
+      <c r="E53" s="112" t="s">
+        <v>344</v>
       </c>
       <c r="F53" s="98"/>
     </row>
     <row r="54" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="C54" s="59" t="s">
         <v>346</v>
-      </c>
-      <c r="C54" s="59" t="s">
-        <v>347</v>
       </c>
       <c r="D54" s="75">
         <f>Inputs!C23*Inputs!C31</f>
         <v>490000</v>
       </c>
-      <c r="E54" s="112" t="s">
-        <v>348</v>
+      <c r="E54" s="113" t="s">
+        <v>347</v>
       </c>
       <c r="F54" s="98"/>
     </row>
     <row r="55" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C55" s="66" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D55" s="75">
         <f>Inputs!C23*Inputs!C31-Inputs!C47</f>
         <v>285250</v>
       </c>
-      <c r="E55" s="113" t="s">
-        <v>350</v>
+      <c r="E55" s="112" t="s">
+        <v>349</v>
       </c>
       <c r="F55" s="98"/>
     </row>
     <row r="56" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C56" s="59" t="s">
+        <v>346</v>
+      </c>
+      <c r="D56" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="C56" s="59" t="s">
-        <v>347</v>
-      </c>
-      <c r="D56" s="18" t="s">
+      <c r="E56" s="113" t="s">
         <v>352</v>
-      </c>
-      <c r="E56" s="112" t="s">
-        <v>353</v>
       </c>
       <c r="F56" s="98"/>
     </row>
     <row r="57" spans="2:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C57" s="66" t="s">
+        <v>346</v>
+      </c>
+      <c r="D57" s="21" t="s">
         <v>354</v>
       </c>
-      <c r="C57" s="66" t="s">
-        <v>347</v>
-      </c>
-      <c r="D57" s="21" t="s">
+      <c r="E57" s="112" t="s">
         <v>355</v>
-      </c>
-      <c r="E57" s="113" t="s">
-        <v>356</v>
       </c>
       <c r="F57" s="98"/>
     </row>
     <row r="58" spans="2:6" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="59" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="100" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="98"/>
@@ -5151,17 +5151,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="D10:F10"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="B46:F46"/>
@@ -5178,10 +5167,21 @@
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="E56:F56"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="D10:F10"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E50:F50"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="E50:F50"/>
     <mergeCell ref="E55:F55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5206,7 +5206,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="101" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="97" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B2" s="98"/>
       <c r="C2" s="98"/>
@@ -5231,7 +5231,7 @@
     <row r="3" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="99" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C4" s="98"/>
       <c r="D4" s="98"/>
@@ -5241,16 +5241,16 @@
     </row>
     <row r="5" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="F5" s="105" t="s">
         <v>218</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="6" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C6" s="74">
         <f>Inputs!C48</f>
@@ -5273,14 +5273,14 @@
         <f>Inputs!C48</f>
         <v>18986500</v>
       </c>
-      <c r="F6" s="108" t="s">
-        <v>363</v>
+      <c r="F6" s="109" t="s">
+        <v>362</v>
       </c>
       <c r="G6" s="98"/>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="B7" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C7" s="77">
         <f>Inputs!C30</f>
@@ -5294,8 +5294,8 @@
         <f>Inputs!C32</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="F7" s="110" t="s">
-        <v>365</v>
+      <c r="F7" s="111" t="s">
+        <v>364</v>
       </c>
       <c r="G7" s="98"/>
     </row>
@@ -5315,14 +5315,14 @@
         <f>Inputs!C33</f>
         <v>0.02</v>
       </c>
-      <c r="F8" s="108" t="s">
-        <v>366</v>
+      <c r="F8" s="109" t="s">
+        <v>365</v>
       </c>
       <c r="G8" s="98"/>
     </row>
     <row r="9" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C9" s="77">
         <f>Inputs!C49</f>
@@ -5336,26 +5336,26 @@
         <f>Inputs!C51</f>
         <v>0.115</v>
       </c>
-      <c r="F9" s="110" t="s">
-        <v>368</v>
+      <c r="F9" s="111" t="s">
+        <v>367</v>
       </c>
       <c r="G9" s="98"/>
     </row>
     <row r="10" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="D10" s="80" t="s">
+        <v>369</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="F10" s="109" t="s">
         <v>370</v>
-      </c>
-      <c r="D10" s="80" t="s">
-        <v>370</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="F10" s="108" t="s">
-        <v>371</v>
       </c>
       <c r="G10" s="98"/>
     </row>
@@ -5375,32 +5375,32 @@
         <f>Inputs!C35</f>
         <v>10000000</v>
       </c>
-      <c r="F11" s="110" t="s">
-        <v>372</v>
+      <c r="F11" s="111" t="s">
+        <v>371</v>
       </c>
       <c r="G11" s="98"/>
     </row>
     <row r="12" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="D12" s="80" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="F12" s="109" t="s">
         <v>374</v>
-      </c>
-      <c r="D12" s="80" t="s">
-        <v>374</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="F12" s="108" t="s">
-        <v>375</v>
       </c>
       <c r="G12" s="98"/>
     </row>
     <row r="13" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C13" s="74">
         <f>Inputs!C47</f>
@@ -5414,15 +5414,15 @@
         <f>Inputs!C47</f>
         <v>204750</v>
       </c>
-      <c r="F13" s="110" t="s">
-        <v>377</v>
+      <c r="F13" s="111" t="s">
+        <v>376</v>
       </c>
       <c r="G13" s="98"/>
     </row>
     <row r="14" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="99" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C15" s="98"/>
       <c r="D15" s="98"/>
@@ -5432,27 +5432,27 @@
     </row>
     <row r="16" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C17" s="66">
         <v>2027</v>
@@ -5470,12 +5470,12 @@
         <v>21169947.5</v>
       </c>
       <c r="G17" s="81" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C18" s="59">
         <v>2028</v>
@@ -5496,7 +5496,7 @@
     </row>
     <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C19" s="66">
         <v>2029</v>
@@ -5517,7 +5517,7 @@
     </row>
     <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C20" s="59">
         <v>2030</v>
@@ -5538,7 +5538,7 @@
     </row>
     <row r="21" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C21" s="84">
         <v>2031</v>
@@ -5556,12 +5556,12 @@
         <v>32720448.696790215</v>
       </c>
       <c r="G21" s="86" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C22" s="59">
         <v>2032</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C23" s="66">
         <v>2033</v>
@@ -5603,7 +5603,7 @@
     </row>
     <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C24" s="59">
         <v>2034</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C25" s="66">
         <v>2035</v>
@@ -5645,7 +5645,7 @@
     </row>
     <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C26" s="87">
         <v>2036</v>
@@ -5663,12 +5663,12 @@
         <v>56388895.42144578</v>
       </c>
       <c r="G26" s="88" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C27" s="66">
         <v>2037</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C28" s="59">
         <v>2038</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C29" s="66">
         <v>2039</v>
@@ -5731,7 +5731,7 @@
     </row>
     <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C30" s="59">
         <v>2040</v>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C31" s="84">
         <v>2041</v>
@@ -5770,12 +5770,12 @@
         <v>97177992.768866569</v>
       </c>
       <c r="G31" s="86" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C32" s="59">
         <v>2042</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C33" s="66">
         <v>2043</v>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C34" s="59">
         <v>2044</v>
@@ -5838,7 +5838,7 @@
     </row>
     <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C35" s="66">
         <v>2045</v>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C36" s="87">
         <v>2046</v>
@@ -5877,12 +5877,12 @@
         <v>167472021.00707078</v>
       </c>
       <c r="G36" s="88" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="40" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C37" s="89">
         <v>2046</v>
@@ -5900,12 +5900,12 @@
         <v>167472021.00707078</v>
       </c>
       <c r="G37" s="40" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="99" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C39" s="98"/>
       <c r="D39" s="98"/>
@@ -5915,19 +5915,19 @@
     </row>
     <row r="40" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>218</v>
@@ -5935,10 +5935,10 @@
     </row>
     <row r="41" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="90" t="s">
+        <v>415</v>
+      </c>
+      <c r="C41" s="59" t="s">
         <v>416</v>
-      </c>
-      <c r="C41" s="59" t="s">
-        <v>417</v>
       </c>
       <c r="D41" s="46">
         <f>Inputs!C23</f>
@@ -5948,18 +5948,18 @@
         <v>0</v>
       </c>
       <c r="F41" s="92" t="s">
+        <v>417</v>
+      </c>
+      <c r="G41" s="47" t="s">
         <v>418</v>
-      </c>
-      <c r="G41" s="47" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="39" x14ac:dyDescent="0.2">
       <c r="B42" s="93" t="s">
+        <v>419</v>
+      </c>
+      <c r="C42" s="66" t="s">
         <v>420</v>
-      </c>
-      <c r="C42" s="66" t="s">
-        <v>421</v>
       </c>
       <c r="D42" s="46">
         <f>Inputs!C23*(1+(Inputs!C36-Inputs!C37))^5+Inputs!C38*((1+(Inputs!C36-Inputs!C37))^5-1)/(Inputs!C36-Inputs!C37)</f>
@@ -5970,18 +5970,18 @@
         <v>1250000</v>
       </c>
       <c r="F42" s="94" t="s">
+        <v>421</v>
+      </c>
+      <c r="G42" s="48" t="s">
         <v>422</v>
-      </c>
-      <c r="G42" s="48" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="26" x14ac:dyDescent="0.2">
       <c r="B43" s="90" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C43" s="59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D43" s="46">
         <f>Inputs!C23*(1+(Inputs!C36-Inputs!C37))^10+Inputs!C38*((1+(Inputs!C36-Inputs!C37))^10-1)/(Inputs!C36-Inputs!C37)</f>
@@ -5992,18 +5992,18 @@
         <v>2500000</v>
       </c>
       <c r="F43" s="92" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G43" s="47" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="26" x14ac:dyDescent="0.2">
       <c r="B44" s="95" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C44" s="66" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D44" s="54">
         <f>Inputs!C23*(1+(Inputs!C36-Inputs!C37))^10+Inputs!C38*((1+(Inputs!C36-Inputs!C37))^10-1)/(Inputs!C36-Inputs!C37)</f>
@@ -6014,18 +6014,18 @@
         <v>2500000</v>
       </c>
       <c r="F44" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="G44" s="48" t="s">
         <v>427</v>
-      </c>
-      <c r="G44" s="48" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="39" x14ac:dyDescent="0.2">
       <c r="B45" s="96" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C45" s="59" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D45" s="54">
         <f>Inputs!C23*(1+(Inputs!C36-Inputs!C37))^20+Inputs!C38*((1+(Inputs!C36-Inputs!C37))^20-1)/(Inputs!C36-Inputs!C37)</f>
@@ -6036,16 +6036,16 @@
         <v>5000000</v>
       </c>
       <c r="F45" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="G45" s="47" t="s">
         <v>430</v>
-      </c>
-      <c r="G45" s="47" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="2:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="100" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C47" s="98"/>
       <c r="D47" s="98"/>
@@ -6055,6 +6055,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="F9:G9"/>
@@ -6065,11 +6070,6 @@
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="F10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
